--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/UTAH_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/UTAH_2022.xlsx
@@ -481,7 +481,7 @@
         <v>7</v>
       </c>
       <c r="D7">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="8">
@@ -2713,7 +2713,7 @@
         <v>7</v>
       </c>
       <c r="D131">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="132">
@@ -2857,7 +2857,7 @@
         <v>7</v>
       </c>
       <c r="D139">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="140">
@@ -3271,7 +3271,7 @@
         <v>7</v>
       </c>
       <c r="D162">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="163">
@@ -4261,7 +4261,7 @@
         <v>7</v>
       </c>
       <c r="D217">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="218">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C239">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C245">
@@ -5053,7 +5053,7 @@
         <v>7</v>
       </c>
       <c r="D261">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="262">
@@ -5341,7 +5341,7 @@
         <v>7</v>
       </c>
       <c r="D277">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="278">
@@ -5485,7 +5485,7 @@
         <v>67</v>
       </c>
       <c r="D285">
-        <v>0.009259259259259259</v>
+        <v>0.00925925925925926</v>
       </c>
     </row>
     <row r="286">
@@ -5575,7 +5575,7 @@
         <v>7</v>
       </c>
       <c r="D290">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="291">
@@ -5737,7 +5737,7 @@
         <v>7</v>
       </c>
       <c r="D299">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="300">
@@ -6187,7 +6187,7 @@
         <v>7</v>
       </c>
       <c r="D324">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="325">
@@ -6583,7 +6583,7 @@
         <v>7</v>
       </c>
       <c r="D346">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="347">
@@ -6781,7 +6781,7 @@
         <v>7</v>
       </c>
       <c r="D357">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="358">
@@ -6817,7 +6817,7 @@
         <v>7</v>
       </c>
       <c r="D359">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="360">
@@ -6925,7 +6925,7 @@
         <v>7</v>
       </c>
       <c r="D365">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="366">
@@ -7321,7 +7321,7 @@
         <v>7</v>
       </c>
       <c r="D387">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="388">
@@ -7825,7 +7825,7 @@
         <v>7</v>
       </c>
       <c r="D415">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="416">
@@ -7969,7 +7969,7 @@
         <v>7</v>
       </c>
       <c r="D423">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="424">
@@ -8401,7 +8401,7 @@
         <v>7</v>
       </c>
       <c r="D447">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="448">
@@ -8473,7 +8473,7 @@
         <v>7</v>
       </c>
       <c r="D451">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="452">
@@ -9229,7 +9229,7 @@
         <v>7</v>
       </c>
       <c r="D493">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="494">
@@ -9553,7 +9553,7 @@
         <v>7</v>
       </c>
       <c r="D511">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="512">
@@ -10129,7 +10129,7 @@
         <v>7</v>
       </c>
       <c r="D543">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="544">
@@ -10471,7 +10471,7 @@
         <v>7</v>
       </c>
       <c r="D562">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="563">
@@ -11335,7 +11335,7 @@
         <v>7</v>
       </c>
       <c r="D610">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="611">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="B663" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C663">
@@ -12642,7 +12642,7 @@
       </c>
       <c r="B683" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C683">
@@ -13621,7 +13621,7 @@
         <v>7</v>
       </c>
       <c r="D737">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="738">
@@ -18337,7 +18337,7 @@
         <v>7</v>
       </c>
       <c r="D999">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="1000">
@@ -18409,7 +18409,7 @@
         <v>7</v>
       </c>
       <c r="D1003">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="1004">
@@ -18463,7 +18463,7 @@
         <v>7</v>
       </c>
       <c r="D1006">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="1007">
@@ -19633,7 +19633,7 @@
         <v>7</v>
       </c>
       <c r="D1071">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="1072">
@@ -19741,7 +19741,7 @@
         <v>7</v>
       </c>
       <c r="D1077">
-        <v>0.0009673852957435047</v>
+        <v>0.0009673852957435048</v>
       </c>
     </row>
     <row r="1078">
